--- a/Carga de Materiales.xlsx
+++ b/Carga de Materiales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RepositoriosAEC\Acrux-Release\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB66AD6-5576-4059-B399-5EA5DF0ED270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20AEDC6-C7B6-438E-8A5C-2B64583754B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="materiales (1)" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>TIPO INVENTARIO</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>STOCK MAX</t>
-  </si>
-  <si>
-    <t>ID EMPRESA</t>
   </si>
   <si>
     <t>ATRIBUTO DINAMICO 1</t>
@@ -995,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -1015,12 +1012,11 @@
     <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="27" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="26" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1102,11 +1098,8 @@
       <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1114,25 +1107,25 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>31</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>34</v>
       </c>
       <c r="J2">
         <v>500</v>
@@ -1158,8 +1151,8 @@
       <c r="Q2">
         <v>150</v>
       </c>
-      <c r="R2">
-        <v>1</v>
+      <c r="R2" t="s">
+        <v>34</v>
       </c>
       <c r="S2" t="s">
         <v>35</v>
@@ -1187,9 +1180,6 @@
       </c>
       <c r="AA2" t="s">
         <v>43</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
